--- a/expert_lista_2026-03-04.xlsx
+++ b/expert_lista_2026-03-04.xlsx
@@ -478,11 +478,11 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -511,11 +511,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -544,11 +544,11 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -577,11 +577,11 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -610,11 +610,11 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -643,11 +643,11 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -709,11 +709,11 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -742,11 +742,11 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Over 1.5 | Corners Over 9.5</t>
+          <t>Over 1.5 | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -775,11 +775,11 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -808,11 +808,11 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -841,11 +841,11 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -874,11 +874,11 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -907,11 +907,11 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Over 1.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -940,11 +940,11 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1006,11 +1006,11 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1039,11 +1039,11 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1072,11 +1072,11 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1105,11 +1105,11 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1138,11 +1138,11 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1171,11 +1171,11 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1204,11 +1204,11 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1237,11 +1237,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1270,11 +1270,11 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1336,11 +1336,11 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1369,11 +1369,11 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1402,11 +1402,11 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1435,11 +1435,11 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1468,11 +1468,11 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Over 1.5 | Corners Over 9.5</t>
+          <t>Over 1.5 | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1534,11 +1534,11 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1600,11 +1600,11 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Over 1.5 | Corners Over 9.5</t>
+          <t>Over 1.5 | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1666,11 +1666,11 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Over 1.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1699,11 +1699,11 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1732,11 +1732,11 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1765,11 +1765,11 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1798,11 +1798,11 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1831,11 +1831,11 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1864,11 +1864,11 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1897,11 +1897,11 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1930,11 +1930,11 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1963,11 +1963,11 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -1996,11 +1996,11 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2029,11 +2029,11 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2062,11 +2062,11 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2095,11 +2095,11 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2128,11 +2128,11 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Over 1.5 | Corners Over 9.5</t>
+          <t>Over 1.5 | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2161,11 +2161,11 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Over 1.5 | Corners Over 9.5</t>
+          <t>Over 1.5 | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2194,11 +2194,11 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2227,11 +2227,11 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2260,11 +2260,11 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2293,11 +2293,11 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2326,11 +2326,11 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2359,11 +2359,11 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2392,11 +2392,11 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2425,11 +2425,11 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2458,11 +2458,11 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2491,11 +2491,11 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2524,11 +2524,11 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2557,11 +2557,11 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2590,11 +2590,11 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2623,11 +2623,11 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2656,11 +2656,11 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2689,11 +2689,11 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2722,11 +2722,11 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2755,11 +2755,11 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2821,11 +2821,11 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2887,11 +2887,11 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2920,11 +2920,11 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2953,11 +2953,11 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -2986,11 +2986,11 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3019,11 +3019,11 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3052,11 +3052,11 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3085,11 +3085,11 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3118,11 +3118,11 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3151,11 +3151,11 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3184,11 +3184,11 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3217,11 +3217,11 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3250,11 +3250,11 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3283,11 +3283,11 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3316,11 +3316,11 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3349,11 +3349,11 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3382,11 +3382,11 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3415,11 +3415,11 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3448,11 +3448,11 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3481,11 +3481,11 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3514,11 +3514,11 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3547,11 +3547,11 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3580,11 +3580,11 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3613,11 +3613,11 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3646,11 +3646,11 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3679,11 +3679,11 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Over 1.5 | Corners Over 9.5</t>
+          <t>Over 1.5 | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3712,11 +3712,11 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3745,11 +3745,11 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3778,11 +3778,11 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3811,11 +3811,11 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3844,11 +3844,11 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3877,11 +3877,11 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3910,11 +3910,11 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3943,11 +3943,11 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -3976,11 +3976,11 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4009,11 +4009,11 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4042,11 +4042,11 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4075,11 +4075,11 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4108,11 +4108,11 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4141,11 +4141,11 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4174,11 +4174,11 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4207,11 +4207,11 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4240,11 +4240,11 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4273,11 +4273,11 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4306,11 +4306,11 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4339,11 +4339,11 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4372,11 +4372,11 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4405,11 +4405,11 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4438,11 +4438,11 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4471,11 +4471,11 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4504,11 +4504,11 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4537,11 +4537,11 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4570,11 +4570,11 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4603,11 +4603,11 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4636,11 +4636,11 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4669,11 +4669,11 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4702,11 +4702,11 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4735,11 +4735,11 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4768,11 +4768,11 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4801,11 +4801,11 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4834,11 +4834,11 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4867,11 +4867,11 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4900,11 +4900,11 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4933,11 +4933,11 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4966,11 +4966,11 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -4999,11 +4999,11 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5032,11 +5032,11 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5065,11 +5065,11 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5098,11 +5098,11 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5131,11 +5131,11 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5164,11 +5164,11 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5197,11 +5197,11 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Over 1.5 | Corners Over 9.5</t>
+          <t>Over 1.5 | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5230,11 +5230,11 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5263,11 +5263,11 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5296,11 +5296,11 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5329,11 +5329,11 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5362,11 +5362,11 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5395,11 +5395,11 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5428,11 +5428,11 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5461,11 +5461,11 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5494,11 +5494,11 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5527,11 +5527,11 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5560,11 +5560,11 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5593,11 +5593,11 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5626,11 +5626,11 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5659,11 +5659,11 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5692,11 +5692,11 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5725,11 +5725,11 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5758,11 +5758,11 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5791,11 +5791,11 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5824,11 +5824,11 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5857,11 +5857,11 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5890,11 +5890,11 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5923,11 +5923,11 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5956,11 +5956,11 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -5989,11 +5989,11 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6022,11 +6022,11 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6055,11 +6055,11 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6088,11 +6088,11 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6154,11 +6154,11 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6187,11 +6187,11 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6220,11 +6220,11 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6253,11 +6253,11 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6286,11 +6286,11 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6319,11 +6319,11 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6352,11 +6352,11 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6385,11 +6385,11 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6418,11 +6418,11 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6451,11 +6451,11 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6484,11 +6484,11 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Over 1.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6517,11 +6517,11 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6550,11 +6550,11 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6583,11 +6583,11 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6616,11 +6616,11 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6649,11 +6649,11 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6682,11 +6682,11 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6715,11 +6715,11 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6748,11 +6748,11 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6781,11 +6781,11 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6814,11 +6814,11 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6847,11 +6847,11 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6880,11 +6880,11 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6913,11 +6913,11 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6946,11 +6946,11 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -6979,11 +6979,11 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7012,11 +7012,11 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7045,11 +7045,11 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7078,11 +7078,11 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7111,11 +7111,11 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7144,11 +7144,11 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7177,11 +7177,11 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7210,11 +7210,11 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7243,11 +7243,11 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7276,11 +7276,11 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7309,11 +7309,11 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7342,11 +7342,11 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7375,11 +7375,11 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7408,11 +7408,11 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7441,11 +7441,11 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7474,11 +7474,11 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7507,11 +7507,11 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7540,11 +7540,11 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7573,11 +7573,11 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7606,11 +7606,11 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7639,11 +7639,11 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7672,11 +7672,11 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7705,11 +7705,11 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7738,11 +7738,11 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7771,11 +7771,11 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7804,11 +7804,11 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Over 1.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7837,11 +7837,11 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7870,11 +7870,11 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7903,11 +7903,11 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7936,11 +7936,11 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -7969,11 +7969,11 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8002,11 +8002,11 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8035,11 +8035,11 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8068,11 +8068,11 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8101,11 +8101,11 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8134,11 +8134,11 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8167,11 +8167,11 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8200,11 +8200,11 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8233,11 +8233,11 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8266,11 +8266,11 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8299,11 +8299,11 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Over 1.5 | Corners Over 9.5</t>
+          <t>Over 1.5 | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8332,11 +8332,11 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8365,11 +8365,11 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8398,11 +8398,11 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8431,11 +8431,11 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8464,11 +8464,11 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8497,11 +8497,11 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8530,11 +8530,11 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8563,11 +8563,11 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8596,11 +8596,11 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8629,11 +8629,11 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8662,11 +8662,11 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8695,11 +8695,11 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8728,11 +8728,11 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8761,11 +8761,11 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8794,11 +8794,11 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8827,11 +8827,11 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8860,11 +8860,11 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Over 1.5 | Corners Over 9.5</t>
+          <t>Over 1.5 | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8893,11 +8893,11 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8926,11 +8926,11 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8959,11 +8959,11 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -8992,11 +8992,11 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9025,11 +9025,11 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9058,11 +9058,11 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9091,11 +9091,11 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9124,11 +9124,11 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9157,11 +9157,11 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9190,11 +9190,11 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9223,11 +9223,11 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9256,11 +9256,11 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Over 1.5 | Corners Over 9.5</t>
+          <t>Over 1.5 | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9289,11 +9289,11 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9322,11 +9322,11 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9355,11 +9355,11 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9388,11 +9388,11 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9421,11 +9421,11 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9454,11 +9454,11 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9487,11 +9487,11 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9520,11 +9520,11 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9553,11 +9553,11 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9586,11 +9586,11 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9619,11 +9619,11 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9652,11 +9652,11 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9685,11 +9685,11 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9718,11 +9718,11 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9751,11 +9751,11 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9784,11 +9784,11 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9817,11 +9817,11 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9850,11 +9850,11 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9883,11 +9883,11 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Over 1.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9916,11 +9916,11 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9949,11 +9949,11 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -9982,11 +9982,11 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10015,11 +10015,11 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10048,11 +10048,11 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10081,11 +10081,11 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Over 1.5 | Corners Over 9.5</t>
+          <t>Over 1.5 | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10114,11 +10114,11 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10147,11 +10147,11 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10180,11 +10180,11 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10213,11 +10213,11 @@
         </is>
       </c>
       <c r="F297" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10246,11 +10246,11 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10279,11 +10279,11 @@
         </is>
       </c>
       <c r="F299" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10312,11 +10312,11 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10345,11 +10345,11 @@
         </is>
       </c>
       <c r="F301" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10378,11 +10378,11 @@
         </is>
       </c>
       <c r="F302" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10411,11 +10411,11 @@
         </is>
       </c>
       <c r="F303" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10444,11 +10444,11 @@
         </is>
       </c>
       <c r="F304" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10477,11 +10477,11 @@
         </is>
       </c>
       <c r="F305" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10510,11 +10510,11 @@
         </is>
       </c>
       <c r="F306" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10543,11 +10543,11 @@
         </is>
       </c>
       <c r="F307" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10576,11 +10576,11 @@
         </is>
       </c>
       <c r="F308" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10609,11 +10609,11 @@
         </is>
       </c>
       <c r="F309" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10642,11 +10642,11 @@
         </is>
       </c>
       <c r="F310" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10675,11 +10675,11 @@
         </is>
       </c>
       <c r="F311" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10708,11 +10708,11 @@
         </is>
       </c>
       <c r="F312" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10741,11 +10741,11 @@
         </is>
       </c>
       <c r="F313" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Over 1.5 | Corners Over 9.5</t>
+          <t>Over 1.5 | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10774,11 +10774,11 @@
         </is>
       </c>
       <c r="F314" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10807,11 +10807,11 @@
         </is>
       </c>
       <c r="F315" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10840,11 +10840,11 @@
         </is>
       </c>
       <c r="F316" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10873,11 +10873,11 @@
         </is>
       </c>
       <c r="F317" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10906,11 +10906,11 @@
         </is>
       </c>
       <c r="F318" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10939,11 +10939,11 @@
         </is>
       </c>
       <c r="F319" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -10972,11 +10972,11 @@
         </is>
       </c>
       <c r="F320" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11005,11 +11005,11 @@
         </is>
       </c>
       <c r="F321" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11038,11 +11038,11 @@
         </is>
       </c>
       <c r="F322" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11071,11 +11071,11 @@
         </is>
       </c>
       <c r="F323" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11104,11 +11104,11 @@
         </is>
       </c>
       <c r="F324" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11137,11 +11137,11 @@
         </is>
       </c>
       <c r="F325" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11170,11 +11170,11 @@
         </is>
       </c>
       <c r="F326" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11203,11 +11203,11 @@
         </is>
       </c>
       <c r="F327" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11236,11 +11236,11 @@
         </is>
       </c>
       <c r="F328" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 9.5</t>
+          <t>Over 2.5 | Over 2.5 &amp; BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11269,11 +11269,11 @@
         </is>
       </c>
       <c r="F329" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11302,11 +11302,11 @@
         </is>
       </c>
       <c r="F330" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11335,11 +11335,11 @@
         </is>
       </c>
       <c r="F331" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11368,11 +11368,11 @@
         </is>
       </c>
       <c r="F332" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11401,11 +11401,11 @@
         </is>
       </c>
       <c r="F333" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11434,11 +11434,11 @@
         </is>
       </c>
       <c r="F334" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11467,11 +11467,11 @@
         </is>
       </c>
       <c r="F335" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11500,11 +11500,11 @@
         </is>
       </c>
       <c r="F336" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11533,11 +11533,11 @@
         </is>
       </c>
       <c r="F337" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>BTTS | Corners Over 9.5</t>
+          <t>BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11566,11 +11566,11 @@
         </is>
       </c>
       <c r="F338" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11599,11 +11599,11 @@
         </is>
       </c>
       <c r="F339" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11632,11 +11632,11 @@
         </is>
       </c>
       <c r="F340" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Corners Over 9.5</t>
+          <t>Corners Over 7.5</t>
         </is>
       </c>
     </row>
@@ -11665,11 +11665,11 @@
         </is>
       </c>
       <c r="F341" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Over 1.5 | BTTS | Corners Over 9.5</t>
+          <t>Over 1.5 | BTTS | Corners Over 7.5</t>
         </is>
       </c>
     </row>
